--- a/Assets/Resources/DATABASE/Database.xlsx
+++ b/Assets/Resources/DATABASE/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tqhie\Unity Projects\Where-To\Assets\Resources\DATABASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47479B5-8391-4797-95D3-08CFB2F8BB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D69FF2E-3E18-42DF-BEF8-57AE4BF7895B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0E7384ED-7C35-4E8F-B735-540A4F72621F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{0E7384ED-7C35-4E8F-B735-540A4F72621F}"/>
   </bookViews>
   <sheets>
     <sheet name="RIDE_REQUEST" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Jimmy</t>
   </si>
   <si>
-    <t>jimmy</t>
-  </si>
-  <si>
     <t>DURATION</t>
   </si>
   <si>
@@ -82,15 +79,6 @@
     <t>apartment</t>
   </si>
   <si>
-    <t>crapfield</t>
-  </si>
-  <si>
-    <t>tyrell</t>
-  </si>
-  <si>
-    <t>warehouse</t>
-  </si>
-  <si>
     <t>SPAWN</t>
   </si>
   <si>
@@ -112,18 +100,9 @@
     <t>001</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
     <t>HANNAH_MET</t>
   </si>
   <si>
@@ -154,9 +133,6 @@
     <t>yay</t>
   </si>
   <si>
-    <t>yo</t>
-  </si>
-  <si>
     <t>SEGMENT</t>
   </si>
   <si>
@@ -166,12 +142,6 @@
     <t>DAY</t>
   </si>
   <si>
-    <t>yar</t>
-  </si>
-  <si>
-    <t>yip</t>
-  </si>
-  <si>
     <t>SHORTCUT_004</t>
   </si>
   <si>
@@ -202,124 +172,25 @@
     <t>TAG</t>
   </si>
   <si>
-    <t>SET_0102/HEY</t>
-  </si>
-  <si>
-    <t>SET_0304/HEY</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>008</t>
-  </si>
-  <si>
     <t>one</t>
   </si>
   <si>
-    <t>two</t>
-  </si>
-  <si>
-    <t>three</t>
-  </si>
-  <si>
-    <t>four</t>
-  </si>
-  <si>
-    <t>five</t>
-  </si>
-  <si>
-    <t>six</t>
-  </si>
-  <si>
-    <t>eight</t>
-  </si>
-  <si>
-    <t>seven</t>
-  </si>
-  <si>
     <t>geton_001</t>
   </si>
   <si>
     <t>end_001</t>
   </si>
   <si>
-    <t>geton_002</t>
-  </si>
-  <si>
-    <t>geton_003</t>
-  </si>
-  <si>
-    <t>geton_004</t>
-  </si>
-  <si>
-    <t>end_002</t>
-  </si>
-  <si>
-    <t>end_003</t>
-  </si>
-  <si>
-    <t>end_004</t>
-  </si>
-  <si>
     <t>during_001</t>
   </si>
   <si>
-    <t>during_002</t>
-  </si>
-  <si>
-    <t>during_003</t>
-  </si>
-  <si>
-    <t>during_004</t>
-  </si>
-  <si>
     <t>transition_001</t>
   </si>
   <si>
-    <t>transition_002</t>
-  </si>
-  <si>
-    <t>transition_003</t>
-  </si>
-  <si>
-    <t>transition_004</t>
-  </si>
-  <si>
     <t>010</t>
-  </si>
-  <si>
-    <t>020</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>040</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>070</t>
-  </si>
-  <si>
-    <t>080</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1665,7 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
@@ -1803,28 +1674,28 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
@@ -1841,34 +1712,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
@@ -1881,39 +1752,17 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="A3" s="12"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -1925,39 +1774,17 @@
       <c r="Z3" s="3"/>
     </row>
     <row r="4" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A4" s="12"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -1969,39 +1796,17 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="A5" s="12"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -2013,39 +1818,17 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="A6" s="12"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -2057,39 +1840,17 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="A7" s="12"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -2101,39 +1862,17 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A8" s="12"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -2145,39 +1884,17 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" spans="1:26" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -3006,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -3037,13 +2754,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -3067,18 +2784,10 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -4000,7 +3709,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE75206-B358-44F7-8367-AB97E19840D2}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="17.33203125" style="3" customWidth="1"/>
@@ -4019,50 +3728,26 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4095,16 +3780,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -4114,83 +3799,47 @@
     </row>
     <row r="2" spans="1:11" s="17" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>78</v>
-      </c>
+      <c r="A3" s="22"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>79</v>
-      </c>
+      <c r="A4" s="22"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>80</v>
-      </c>
+      <c r="A5" s="22"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -4228,7 +3877,7 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="B1" s="30" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="10"/>
@@ -4240,25 +3889,25 @@
     </row>
     <row r="2" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="12" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="31"/>
       <c r="B4" s="12" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -4266,28 +3915,28 @@
     </row>
     <row r="6" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="31"/>
       <c r="B7" s="12" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="31"/>
       <c r="B8" s="12" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
       <c r="B9" s="12" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -4295,13 +3944,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="31"/>
       <c r="B11" s="12" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -4309,13 +3958,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="31"/>
       <c r="B13" s="12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
